--- a/data/reports/2024-04-01/2024-04-01_duplicates.xlsx
+++ b/data/reports/2024-04-01/2024-04-01_duplicates.xlsx
@@ -140,7 +140,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ff8966501bb7f810027562cae54bcb7f&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004801</t>
+    <t>RMD0004807</t>
   </si>
   <si>
     <t>E-Vergent.Com LLC</t>
@@ -153,12 +153,6 @@
     <t>none</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004807</t>
-  </si>
-  <si>
     <t>Shawn Tarlo</t>
   </si>
   <si>
@@ -184,7 +178,13 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005143</t>
+    <t>RMD0004801</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004495</t>
   </si>
   <si>
     <t>Ooma, Inc.</t>
@@ -195,6 +195,30 @@
 SUNNYVALE CA 94085</t>
   </si>
   <si>
+    <t>0023473408; 0025715012; 0028440600; 0021330824; 0022722623</t>
+  </si>
+  <si>
+    <t>Tobin Farrand</t>
+  </si>
+  <si>
+    <t>Vice President, Engineering &amp; Operations</t>
+  </si>
+  <si>
+    <t>Engineering &amp; Operations</t>
+  </si>
+  <si>
+    <t>6505666600</t>
+  </si>
+  <si>
+    <t>2024-02-26</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cff38bf91b05f4109294113d9c4bcb69&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005143</t>
+  </si>
+  <si>
     <t>0023473408
 0025715012
 0028440600</t>
@@ -213,31 +237,7 @@
 SUNNYVALE CA 94085</t>
   </si>
   <si>
-    <t>6505666600</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b165a0c21b0e3410503110ad9c4bcbce&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004495</t>
-  </si>
-  <si>
-    <t>0023473408; 0025715012; 0028440600; 0021330824; 0022722623</t>
-  </si>
-  <si>
-    <t>Tobin Farrand</t>
-  </si>
-  <si>
-    <t>Vice President, Engineering &amp; Operations</t>
-  </si>
-  <si>
-    <t>Engineering &amp; Operations</t>
-  </si>
-  <si>
-    <t>2024-02-26</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cff38bf91b05f4109294113d9c4bcb69&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005813</t>
@@ -280,7 +280,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009352</t>
+    <t>RMD0004139</t>
   </si>
   <si>
     <t>Global Net Holdings, Inc.</t>
@@ -296,28 +296,28 @@
     <t>CEO</t>
   </si>
   <si>
+    <t>Sales</t>
+  </si>
+  <si>
+    <t>800-709-6314</t>
+  </si>
+  <si>
+    <t>2024-03-29</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009352</t>
+  </si>
+  <si>
     <t>Financial</t>
   </si>
   <si>
     <t>800-7096314</t>
   </si>
   <si>
-    <t>2024-03-29</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004139</t>
-  </si>
-  <si>
-    <t>Sales</t>
-  </si>
-  <si>
-    <t>800-709-6314</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c77b62251b09741002beea82f54bcb87&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008972</t>
@@ -427,7 +427,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0006774</t>
+    <t>RMD0008869</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -437,40 +437,40 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>Sage Network &amp; Communications</t>
+  </si>
+  <si>
+    <t>Rick Minyard</t>
+  </si>
+  <si>
+    <t>Officer</t>
+  </si>
+  <si>
+    <t>Exec</t>
+  </si>
+  <si>
+    <t>8059141801</t>
+  </si>
+  <si>
+    <t>1855</t>
+  </si>
+  <si>
+    <t>2024-02-02</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0006774</t>
+  </si>
+  <si>
     <t>NONE</t>
   </si>
   <si>
-    <t>Sage Network &amp; Communications</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008869</t>
-  </si>
-  <si>
-    <t>Rick Minyard</t>
-  </si>
-  <si>
-    <t>Officer</t>
-  </si>
-  <si>
-    <t>Exec</t>
-  </si>
-  <si>
-    <t>8059141801</t>
-  </si>
-  <si>
-    <t>1855</t>
-  </si>
-  <si>
-    <t>2024-02-02</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003929</t>
+    <t>RMD0004389</t>
   </si>
   <si>
     <t>Idealtel Dominicana USA, Inc. dba myidealtel.com</t>
@@ -481,16 +481,16 @@
 Cooper City FL 33328</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003929</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fab855e51b09741064c4426de54bcbf6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004389</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9a075a791b8db4109294113d9c4bcbd5&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005819</t>
+    <t>RMD0004724</t>
   </si>
   <si>
     <t>Ton80 Communications, LLC</t>
@@ -500,16 +500,16 @@
 Anderson SC 29642</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005819</t>
+  </si>
+  <si>
     <t>4109121000</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=aab7f5961b667c10dabd2f41f54bcb9f&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004724</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004806</t>
@@ -550,10 +550,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=beda02fb1bc5f05064c4426de54bcb94&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -564,20 +574,33 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+    <t>RMD0003758</t>
+  </si>
+  <si>
+    <t>Matchcom Telecommunications Inc.</t>
+  </si>
+  <si>
+    <t>1680 Michigan Ave
+Ste 700
+Miami Beach Florida 33139</t>
+  </si>
+  <si>
+    <t>Davon Person</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Network Operations Center</t>
+  </si>
+  <si>
+    <t>9546248162</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007488</t>
-  </si>
-  <si>
-    <t>Matchcom Telecommunications Inc.</t>
   </si>
   <si>
     <t>1680 Michigan Ave
@@ -611,33 +634,30 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=267cc9661b3ef410aa3cea41f54bcbcd&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003758</t>
-  </si>
-  <si>
-    <t>1680 Michigan Ave
-Ste 700
-Miami Beach Florida 33139</t>
-  </si>
-  <si>
-    <t>Davon Person</t>
-  </si>
-  <si>
-    <t>Director of Operations</t>
-  </si>
-  <si>
-    <t>Network Operations Center</t>
-  </si>
-  <si>
-    <t>9546248162</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
+    <t>RMD0008297</t>
+  </si>
+  <si>
+    <t>GloTell US Corp.</t>
+  </si>
+  <si>
+    <t>1830 S Ocean Drive
+Suite 902
+Halladale Beach FL 33009</t>
+  </si>
+  <si>
+    <t>Alina Karpova</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>9548354110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0002900</t>
-  </si>
-  <si>
-    <t>GloTell US Corp.</t>
   </si>
   <si>
     <t>1001 North Federal Hwy
@@ -664,26 +684,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0a82aeaf1b7430507ccf20ecac4bcb54&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008297</t>
-  </si>
-  <si>
-    <t>1830 S Ocean Drive
-Suite 902
-Halladale Beach FL 33009</t>
-  </si>
-  <si>
-    <t>Alina Karpova</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>9548354110</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0009294</t>
   </si>
   <si>
@@ -760,7 +760,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005124</t>
+    <t>RMD0005139</t>
   </si>
   <si>
     <t>Opentact Inc</t>
@@ -771,12 +771,6 @@
 Cheyenne WY 82009</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005139</t>
-  </si>
-  <si>
     <t>Anne Kwong</t>
   </si>
   <si>
@@ -799,6 +793,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005124</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f40ce7d11b8eb01068d1a82eac4bcbde&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0004701</t>
   </si>
   <si>
@@ -845,7 +845,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003053</t>
+    <t>RMD0009640</t>
   </si>
   <si>
     <t>The Kalson Inc Limited</t>
@@ -855,22 +855,22 @@
  UB10 0AD UXBRIDGE, United Kingdom</t>
   </si>
   <si>
+    <t>Anum Rasheed Kalson</t>
+  </si>
+  <si>
+    <t>'+92-3222100249</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003053</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=73375fbb1b30b0507ccf20ecac4bcb1c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009640</t>
-  </si>
-  <si>
-    <t>Anum Rasheed Kalson</t>
-  </si>
-  <si>
-    <t>'+92-3222100249</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
+    <t>RMD0003444</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -881,6 +881,32 @@
   </si>
   <si>
     <t>Canada</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -900,33 +926,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007384</t>
+    <t>RMD0003705</t>
   </si>
   <si>
     <t>Axkan Consultores S. de R.L. de C.V.</t>
@@ -939,6 +939,12 @@
     <t>Mexico</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007384</t>
+  </si>
+  <si>
     <t>Juan Carlos Bravo Abarca</t>
   </si>
   <si>
@@ -946,12 +952,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=47035e5e1b7eb4109ac2ea04bc4bcbb1&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003705</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009817</t>
@@ -1061,7 +1061,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=93ebdbd01b227810ca5aec21f54bcbd6&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
+    <t>RMD0007936</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -1074,22 +1074,22 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Syed Omar Farooq Shah</t>
+  </si>
+  <si>
+    <t>'+61406851546</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005297</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
-  </si>
-  <si>
-    <t>Syed Omar Farooq Shah</t>
-  </si>
-  <si>
-    <t>'+61406851546</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -1103,6 +1103,18 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -1116,19 +1128,29 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+    <t>RMD0007962</t>
+  </si>
+  <si>
+    <t>office no 17 3rd floor anique arcade pla
+federal 46000 Islamabad, Pakistan</t>
+  </si>
+  <si>
+    <t>Pakistan</t>
+  </si>
+  <si>
+    <t>Umair Hassan</t>
+  </si>
+  <si>
+    <t>Executive</t>
+  </si>
+  <si>
+    <t>'+92-333-6778-636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0006284</t>
@@ -1138,29 +1160,7 @@
   Islamabad, Pakistan</t>
   </si>
   <si>
-    <t>Pakistan</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007962</t>
-  </si>
-  <si>
-    <t>office no 17 3rd floor anique arcade pla
-federal 46000 Islamabad, Pakistan</t>
-  </si>
-  <si>
-    <t>Umair Hassan</t>
-  </si>
-  <si>
-    <t>Executive</t>
-  </si>
-  <si>
-    <t>'+92-333-6778-636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8037e23e1b32781093d3a820f54bcb1c&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008125</t>
@@ -1192,7 +1192,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007575</t>
+    <t>RMD0007626</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1205,16 +1205,16 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007575</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007626</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1224,16 +1224,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1243,6 +1243,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1255,13 +1261,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008097</t>
+    <t>RMD0008064</t>
   </si>
   <si>
     <t>Sam Asher Computing Services, Inc.</t>
@@ -1276,6 +1276,12 @@
 Hyper-Reach</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008097</t>
+  </si>
+  <si>
     <t>Caitlin Olfano</t>
   </si>
   <si>
@@ -1288,13 +1294,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4172e7f21b7a3810dcd1ed3be54bcbb5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008064</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=39639b3a1b3a3810dcd1ed3be54bcb5e&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008393</t>
+    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T. Inc.</t>
@@ -1302,12 +1302,6 @@
   <si>
     <t>295 Weber St. N
 Ontario N2J 3H8 Waterloo, Canada</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008423</t>
   </si>
   <si>
     <t>Your Business I.T.</t>
@@ -1325,6 +1319,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=761bc9e71b3eb810d39dddb6bc4bcbe0&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008393</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008451</t>
   </si>
   <si>
@@ -1344,7 +1344,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008611</t>
+    <t>RMD0008612</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1354,6 +1354,21 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008611</t>
+  </si>
+  <si>
     <t>Bangladesh</t>
   </si>
   <si>
@@ -1369,44 +1384,29 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008756</t>
+    <t>RMD0008759</t>
   </si>
   <si>
     <t>573 Ocean Blvd
 Hampton NH 03842</t>
   </si>
   <si>
+    <t>Jeffrey D Houston</t>
+  </si>
+  <si>
+    <t>6039294272</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008756</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008759</t>
-  </si>
-  <si>
-    <t>Jeffrey D Houston</t>
-  </si>
-  <si>
-    <t>6039294272</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=46724d021b0b3050003c43f1f54bcb05&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008755</t>
@@ -1473,7 +1473,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3752aec61b0f3050003c43f1f54bcb54&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009160</t>
+    <t>RMD0009161</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1483,16 +1483,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>9497014500</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009160</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009161</t>
-  </si>
-  <si>
-    <t>9497014500</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -1527,7 +1527,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=af63c18f1b3bb010c8e0ed3ce54bcb41&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009728</t>
+    <t>RMD0009729</t>
   </si>
   <si>
     <t>Huffman Telcom Corp</t>
@@ -1537,22 +1537,22 @@
 Fort Collins CO 80524</t>
   </si>
   <si>
+    <t>Charlie Huffman</t>
+  </si>
+  <si>
+    <t>Customer Services</t>
+  </si>
+  <si>
+    <t>'+13033140978</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009728</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=a48d8f371bac051085edebdbac4bcbba&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009729</t>
-  </si>
-  <si>
-    <t>Charlie Huffman</t>
-  </si>
-  <si>
-    <t>Customer Services</t>
-  </si>
-  <si>
-    <t>'+13033140978</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dfd83771bac051085edebdbac4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0011742</t>
@@ -6021,31 +6021,47 @@
       <c r="I5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R5" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U5" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="V5" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1">
         <v>16082927</v>
@@ -6071,40 +6087,24 @@
       <c r="I6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
         <v>53</v>
       </c>
@@ -6142,29 +6142,29 @@
       <c r="L7" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="1"/>
+      <c r="N7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U7" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V7" s="1" t="s">
         <v>63</v>
       </c>
@@ -6202,29 +6202,29 @@
       <c r="L8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="N8" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>69</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="U8" s="1"/>
       <c r="V8" s="1" t="s">
         <v>70</v>
       </c>
@@ -6358,15 +6358,9 @@
       <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
       <c r="J11" s="1" t="s">
         <v>87</v>
       </c>
@@ -6387,7 +6381,7 @@
       </c>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>26</v>
@@ -6424,9 +6418,15 @@
       <c r="F12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
+      <c r="G12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J12" s="1" t="s">
         <v>87</v>
       </c>
@@ -6447,7 +6447,7 @@
       </c>
       <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>26</v>
@@ -6800,38 +6800,54 @@
       <c r="F19" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
+      <c r="K19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R19" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U19" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="V19" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B20" s="1">
         <v>23250467</v>
@@ -6848,47 +6864,31 @@
       <c r="F20" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="H20" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I20" s="1"/>
-      <c r="J20" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S20" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>142</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
         <v>143</v>
       </c>
@@ -7003,28 +7003,14 @@
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>153</v>
-      </c>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
       <c r="P23" s="1"/>
-      <c r="Q23" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q23" s="1"/>
       <c r="R23" s="1" t="s">
         <v>29</v>
       </c>
@@ -7032,16 +7018,16 @@
         <v>29</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B24" s="1">
         <v>25462672</v>
@@ -7061,14 +7047,28 @@
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
+      <c r="J24" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>155</v>
+      </c>
       <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
+      <c r="Q24" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R24" s="1" t="s">
         <v>29</v>
       </c>
@@ -7076,7 +7076,7 @@
         <v>29</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1" t="s">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>29</v>
@@ -7308,40 +7308,34 @@
       <c r="L29" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="1"/>
+      <c r="N29" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="N29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O29" s="1" t="s">
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U29" s="1"/>
+      <c r="V29" s="1" t="s">
         <v>183</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B30" s="1">
         <v>27710730</v>
@@ -7350,7 +7344,7 @@
         <v>177</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>29</v>
@@ -7362,35 +7356,41 @@
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="M30" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="N30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="U30" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1"/>
       <c r="V30" s="1" t="s">
         <v>193</v>
       </c>
@@ -7415,47 +7415,47 @@
         <v>33</v>
       </c>
       <c r="G31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>197</v>
-      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="M31" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
+      <c r="Q31" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R31" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U31" s="1"/>
       <c r="V31" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B32" s="1">
         <v>27967686</v>
@@ -7464,7 +7464,7 @@
         <v>195</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>29</v>
@@ -7473,19 +7473,21 @@
         <v>33</v>
       </c>
       <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="I32" s="1"/>
       <c r="J32" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K32" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="L32" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M32" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="N32" s="1" t="s">
         <v>33</v>
@@ -7494,17 +7496,15 @@
         <v>207</v>
       </c>
       <c r="P32" s="1"/>
-      <c r="Q32" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S32" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U32" s="1"/>
       <c r="V32" s="1" t="s">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="P34" s="1"/>
       <c r="Q34" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>26</v>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>26</v>
@@ -7757,31 +7757,47 @@
       <c r="I37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
+      <c r="J37" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
+      <c r="Q37" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R37" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U37" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U37" s="1" t="s">
+        <v>240</v>
+      </c>
       <c r="V37" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B38" s="1">
         <v>30149645</v>
@@ -7807,40 +7823,24 @@
       <c r="I38" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>241</v>
-      </c>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q38" s="1"/>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>242</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
         <v>243</v>
       </c>
@@ -7887,7 +7887,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -7925,13 +7925,13 @@
         <v>255</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J40" s="1" t="s">
         <v>247</v>
@@ -7989,31 +7989,45 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="J41" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="Q41" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R41" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B42" s="1">
         <v>31063506</v>
@@ -8033,36 +8047,22 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>265</v>
-      </c>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8095,31 +8095,45 @@
       <c r="I43" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
+      <c r="J43" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>276</v>
+      </c>
       <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
+      <c r="Q43" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R43" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B44" s="1">
         <v>31064850</v>
@@ -8137,42 +8151,28 @@
         <v>270</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O44" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="J44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
       <c r="P44" s="1"/>
-      <c r="Q44" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q44" s="1"/>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8201,45 +8201,31 @@
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
-      <c r="J45" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>287</v>
-      </c>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
       <c r="P45" s="1"/>
-      <c r="Q45" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="Q45" s="1"/>
       <c r="R45" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="46" spans="1:22">
       <c r="A46" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B46" s="1">
         <v>31092349</v>
@@ -8259,22 +8245,36 @@
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
+      <c r="J46" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>289</v>
+      </c>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
+      <c r="Q46" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R46" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U46" s="1"/>
       <c r="V46" s="1" t="s">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="P51" s="1"/>
       <c r="Q51" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R51" s="1" t="s">
         <v>26</v>
@@ -8629,31 +8629,45 @@
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>330</v>
+      </c>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
+      <c r="Q53" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R53" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B54" s="1">
         <v>31294614</v>
@@ -8673,36 +8687,22 @@
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>332</v>
-      </c>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="M54" s="1"/>
+      <c r="N54" s="1"/>
+      <c r="O54" s="1"/>
       <c r="P54" s="1"/>
-      <c r="Q54" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q54" s="1"/>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8734,48 +8734,40 @@
       <c r="H55" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1" t="s">
+      <c r="I55" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="J55" s="1"/>
+      <c r="K55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>339</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L55" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>342</v>
       </c>
       <c r="P55" s="1"/>
       <c r="Q55" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="R55" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S55" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="56" spans="1:22">
       <c r="A56" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B56" s="1">
         <v>31356652</v>
@@ -8796,35 +8788,43 @@
         <v>337</v>
       </c>
       <c r="H56" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L56" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="M56" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
       <c r="N56" s="1" t="s">
         <v>33</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="P56" s="1"/>
       <c r="Q56" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="R56" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S56" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U56" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="U56" s="1" t="s">
+        <v>91</v>
+      </c>
       <c r="V56" s="1" t="s">
         <v>346</v>
       </c>
@@ -8846,47 +8846,55 @@
       <c r="F57" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="L57" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>352</v>
+      </c>
       <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
+      <c r="Q57" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R57" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B58" s="1">
         <v>31392434</v>
       </c>
       <c r="C58" s="1"/>
       <c r="D58" s="1" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>26</v>
@@ -8894,39 +8902,31 @@
       <c r="F58" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>355</v>
-      </c>
+      <c r="G58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="J58" s="1"/>
+      <c r="K58" s="1"/>
+      <c r="L58" s="1"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
       <c r="P58" s="1"/>
-      <c r="Q58" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q58" s="1"/>
       <c r="R58" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
@@ -8962,7 +8962,7 @@
         <v>361</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>359</v>
@@ -8974,10 +8974,10 @@
         <v>362</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R59" s="1" t="s">
         <v>26</v>
@@ -9144,9 +9144,15 @@
       <c r="F63" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>43</v>
+      </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -9188,15 +9194,9 @@
       <c r="F64" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -9233,55 +9233,39 @@
         <v>381</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
-      <c r="J65" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="P65" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J65" s="1"/>
+      <c r="K65" s="1"/>
+      <c r="L65" s="1"/>
+      <c r="M65" s="1"/>
+      <c r="N65" s="1"/>
+      <c r="O65" s="1"/>
+      <c r="P65" s="1"/>
+      <c r="Q65" s="1"/>
       <c r="R65" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S65" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="66" spans="1:22">
       <c r="A66" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B66" s="1">
         <v>31445216</v>
@@ -9293,30 +9277,46 @@
         <v>381</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
+      <c r="J66" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R66" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T66" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U66" s="1"/>
       <c r="V66" s="1" t="s">
@@ -9337,55 +9337,41 @@
         <v>390</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
         <v>391</v>
       </c>
       <c r="I67" s="1"/>
-      <c r="J67" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>393</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>394</v>
-      </c>
+      <c r="J67" s="1"/>
+      <c r="K67" s="1"/>
+      <c r="L67" s="1"/>
+      <c r="M67" s="1"/>
+      <c r="N67" s="1"/>
+      <c r="O67" s="1"/>
       <c r="P67" s="1"/>
-      <c r="Q67" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q67" s="1"/>
       <c r="R67" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S67" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="68" spans="1:22">
       <c r="A68" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B68" s="1">
         <v>31447154</v>
@@ -9397,32 +9383,46 @@
         <v>390</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
         <v>391</v>
       </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>396</v>
+      </c>
       <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+      <c r="Q68" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U68" s="1"/>
       <c r="V68" s="1" t="s">
@@ -9451,31 +9451,43 @@
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+      <c r="J69" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
+      <c r="M69" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>403</v>
+      </c>
       <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
+      <c r="Q69" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R69" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="70" spans="1:22">
       <c r="A70" s="1" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B70" s="1">
         <v>31455868</v>
@@ -9495,34 +9507,22 @@
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
-      <c r="J70" s="1" t="s">
-        <v>403</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>361</v>
-      </c>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
       <c r="L70" s="1"/>
-      <c r="M70" s="1" t="s">
-        <v>404</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>405</v>
-      </c>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
       <c r="P70" s="1"/>
-      <c r="Q70" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q70" s="1"/>
       <c r="R70" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T70" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U70" s="1"/>
       <c r="V70" s="1" t="s">
@@ -9638,34 +9638,46 @@
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="1"/>
+      <c r="J73" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
+      <c r="K73" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>418</v>
+      </c>
       <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
+      <c r="Q73" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R73" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U73" s="1"/>
       <c r="V73" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="74" spans="1:22">
       <c r="A74" s="1" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B74" s="1">
         <v>31475270</v>
@@ -9680,11 +9692,13 @@
         <v>26</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="G74" s="1"/>
       <c r="H74" s="1"/>
-      <c r="I74" s="1"/>
+      <c r="I74" s="1" t="s">
+        <v>422</v>
+      </c>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -9704,12 +9718,12 @@
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="75" spans="1:22">
       <c r="A75" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B75" s="1">
         <v>31475270</v>
@@ -9724,41 +9738,27 @@
         <v>26</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
-      <c r="J75" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="L75" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>424</v>
-      </c>
+      <c r="J75" s="1"/>
+      <c r="K75" s="1"/>
+      <c r="L75" s="1"/>
+      <c r="M75" s="1"/>
+      <c r="N75" s="1"/>
+      <c r="O75" s="1"/>
       <c r="P75" s="1"/>
-      <c r="Q75" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q75" s="1"/>
       <c r="R75" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T75" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U75" s="1"/>
       <c r="V75" s="1" t="s">
@@ -9777,39 +9777,53 @@
         <v>427</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G76" s="1"/>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
+      <c r="J76" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>361</v>
+      </c>
       <c r="L76" s="1"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
+      <c r="M76" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>80</v>
+      </c>
       <c r="R76" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S76" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U76" s="1"/>
       <c r="V76" s="1" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="77" spans="1:22">
       <c r="A77" s="1" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B77" s="1">
         <v>31485048</v>
@@ -9819,44 +9833,30 @@
         <v>427</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G77" s="1"/>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
-      <c r="J77" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>361</v>
-      </c>
+      <c r="J77" s="1"/>
+      <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="P77" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
       <c r="R77" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T77" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U77" s="1"/>
       <c r="V77" s="1" t="s">
@@ -10058,10 +10058,10 @@
         <v>453</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="Q81" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R81" s="1" t="s">
         <v>26</v>
@@ -10073,7 +10073,7 @@
         <v>29</v>
       </c>
       <c r="U81" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V81" s="1" t="s">
         <v>454</v>
@@ -10093,39 +10093,49 @@
         <v>457</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
+      <c r="J82" s="1" t="s">
+        <v>456</v>
+      </c>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
-      <c r="N82" s="1"/>
-      <c r="O82" s="1"/>
+      <c r="M82" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>458</v>
+      </c>
       <c r="P82" s="1"/>
-      <c r="Q82" s="1"/>
+      <c r="Q82" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="R82" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T82" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U82" s="1"/>
       <c r="V82" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="83" spans="1:22">
       <c r="A83" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B83" s="1">
         <v>31544182</v>
@@ -10137,40 +10147,30 @@
         <v>457</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
-      <c r="J83" s="1" t="s">
-        <v>456</v>
-      </c>
+      <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
-      <c r="M83" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>460</v>
-      </c>
+      <c r="M83" s="1"/>
+      <c r="N83" s="1"/>
+      <c r="O83" s="1"/>
       <c r="P83" s="1"/>
-      <c r="Q83" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="Q83" s="1"/>
       <c r="R83" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T83" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U83" s="1"/>
       <c r="V83" s="1" t="s">
@@ -10293,39 +10293,53 @@
         <v>474</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="1"/>
-      <c r="M86" s="1"/>
-      <c r="N86" s="1"/>
-      <c r="O86" s="1"/>
+      <c r="J86" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="L86" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>477</v>
+      </c>
       <c r="P86" s="1"/>
-      <c r="Q86" s="1"/>
+      <c r="Q86" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="R86" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T86" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U86" s="1"/>
       <c r="V86" s="1" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="87" spans="1:22">
       <c r="A87" s="1" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B87" s="1">
         <v>31758865</v>
@@ -10337,44 +10351,30 @@
         <v>474</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G87" s="1"/>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
-      <c r="J87" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="L87" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="M87" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>479</v>
-      </c>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1"/>
+      <c r="L87" s="1"/>
+      <c r="M87" s="1"/>
+      <c r="N87" s="1"/>
+      <c r="O87" s="1"/>
       <c r="P87" s="1"/>
-      <c r="Q87" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q87" s="1"/>
       <c r="R87" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>29</v>
       </c>
       <c r="T87" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U87" s="1"/>
       <c r="V87" s="1" t="s">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>26</v>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="P89" s="1"/>
       <c r="Q89" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R89" s="1" t="s">
         <v>26</v>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R90" s="1" t="s">
         <v>26</v>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="P92" s="1"/>
       <c r="Q92" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R92" s="1" t="s">
         <v>26</v>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R94" s="1" t="s">
         <v>26</v>
@@ -11159,7 +11159,7 @@
         <v>29</v>
       </c>
       <c r="U101" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V101" s="1" t="s">
         <v>564</v>
@@ -11187,7 +11187,7 @@
         <v>567</v>
       </c>
       <c r="I102" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J102" s="1" t="s">
         <v>568</v>
@@ -11319,7 +11319,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>26</v>
@@ -11428,7 +11428,7 @@
         <v>589</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>595</v>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R107" s="1" t="s">
         <v>26</v>
@@ -11544,7 +11544,7 @@
         <v>321</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>610</v>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R108" s="1" t="s">
         <v>26</v>
@@ -11591,13 +11591,13 @@
         <v>33</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H109" s="1" t="s">
         <v>615</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>616</v>
@@ -11621,7 +11621,7 @@
         <v>619</v>
       </c>
       <c r="Q109" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R109" s="1" t="s">
         <v>26</v>
@@ -11668,7 +11668,7 @@
         <v>321</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M110" s="1"/>
       <c r="N110" s="1" t="s">
@@ -11679,7 +11679,7 @@
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R110" s="1" t="s">
         <v>26</v>
@@ -11741,7 +11741,7 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R111" s="1" t="s">
         <v>26</v>
@@ -11799,7 +11799,7 @@
       </c>
       <c r="P112" s="1"/>
       <c r="Q112" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>26</v>
@@ -11833,13 +11833,13 @@
         <v>33</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H113" s="1" t="s">
         <v>640</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="P114" s="1"/>
       <c r="Q114" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R114" s="1" t="s">
         <v>26</v>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R115" s="1" t="s">
         <v>26</v>
@@ -12058,7 +12058,7 @@
         <v>321</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>662</v>
@@ -12100,7 +12100,7 @@
         <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G118" s="1"/>
       <c r="H118" s="1"/>
@@ -12118,7 +12118,7 @@
         <v>668</v>
       </c>
       <c r="N118" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O118" s="1" t="s">
         <v>669</v>
@@ -12221,13 +12221,13 @@
         <v>33</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>680</v>
@@ -12417,7 +12417,7 @@
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R123" s="1" t="s">
         <v>26</v>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R124" s="1" t="s">
         <v>26</v>
@@ -12521,7 +12521,7 @@
         <v>711</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>110</v>
@@ -12537,7 +12537,7 @@
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R125" s="1" t="s">
         <v>26</v>
@@ -12591,7 +12591,7 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R126" s="1" t="s">
         <v>26</v>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="P130" s="1"/>
       <c r="Q130" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R130" s="1" t="s">
         <v>26</v>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="P131" s="1"/>
       <c r="Q131" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R131" s="1" t="s">
         <v>26</v>
@@ -12912,7 +12912,7 @@
         <v>88</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>752</v>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>26</v>
@@ -13008,7 +13008,7 @@
         <v>26</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G134" s="1"/>
       <c r="H134" s="1"/>
@@ -13073,7 +13073,7 @@
       </c>
       <c r="P135" s="1"/>
       <c r="Q135" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R135" s="1" t="s">
         <v>26</v>
@@ -13135,7 +13135,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>26</v>
@@ -13169,13 +13169,13 @@
         <v>33</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H137" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J137" s="1" t="s">
         <v>779</v>
@@ -13197,7 +13197,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>26</v>
@@ -13270,7 +13270,7 @@
         <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G139" s="1"/>
       <c r="H139" s="1"/>
@@ -13310,7 +13310,7 @@
         <v>26</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>43</v>
@@ -13473,7 +13473,7 @@
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R143" s="1" t="s">
         <v>26</v>
@@ -13560,7 +13560,7 @@
         <v>88</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>808</v>
@@ -13573,7 +13573,7 @@
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>26</v>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R146" s="1" t="s">
         <v>29</v>
@@ -13689,7 +13689,7 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R147" s="1" t="s">
         <v>26</v>
@@ -13803,7 +13803,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R149" s="1" t="s">
         <v>26</v>
@@ -13861,7 +13861,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R150" s="1" t="s">
         <v>26</v>
@@ -13890,7 +13890,7 @@
         <v>26</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -13908,7 +13908,7 @@
         <v>848</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>849</v>
@@ -14096,7 +14096,7 @@
         <v>321</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>867</v>
@@ -14109,7 +14109,7 @@
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R155" s="1" t="s">
         <v>26</v>
@@ -14169,7 +14169,7 @@
       </c>
       <c r="P156" s="1"/>
       <c r="Q156" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R156" s="1" t="s">
         <v>26</v>
@@ -14212,7 +14212,7 @@
         <v>441</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>880</v>
@@ -14225,7 +14225,7 @@
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R157" s="1" t="s">
         <v>26</v>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="P160" s="1"/>
       <c r="Q160" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R160" s="1" t="s">
         <v>26</v>
@@ -14405,7 +14405,7 @@
         <v>897</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L161" s="1" t="s">
         <v>898</v>
@@ -14460,10 +14460,10 @@
       </c>
       <c r="I162" s="1"/>
       <c r="J162" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>904</v>
@@ -14479,7 +14479,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>26</v>
@@ -14521,10 +14521,10 @@
         <v>910</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M163" s="1"/>
       <c r="N163" s="1" t="s">
@@ -14569,7 +14569,7 @@
         <v>33</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H164" s="1"/>
       <c r="I164" s="1"/>
@@ -14712,7 +14712,7 @@
         <v>26</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>43</v>
@@ -14736,7 +14736,7 @@
         <v>930</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O167" s="1" t="s">
         <v>931</v>
@@ -14794,7 +14794,7 @@
         <v>321</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M168" s="1" t="s">
         <v>935</v>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="P169" s="1"/>
       <c r="Q169" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R169" s="1" t="s">
         <v>26</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>29</v>
@@ -15221,7 +15221,7 @@
         <v>981</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R176" s="1" t="s">
         <v>26</v>
@@ -15255,7 +15255,7 @@
         <v>33</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H177" s="1" t="s">
         <v>984</v>
@@ -15337,7 +15337,7 @@
       </c>
       <c r="P178" s="1"/>
       <c r="Q178" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>26</v>
@@ -15384,7 +15384,7 @@
         <v>109</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>998</v>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>26</v>
@@ -15494,7 +15494,7 @@
         <v>1011</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M181" s="1"/>
       <c r="N181" s="1" t="s">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>26</v>
@@ -15594,7 +15594,7 @@
         <v>26</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G183" s="1"/>
       <c r="H183" s="1"/>
@@ -15647,7 +15647,7 @@
         <v>1027</v>
       </c>
       <c r="K184" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L184" s="1" t="s">
         <v>110</v>
@@ -15956,7 +15956,7 @@
         <v>26</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G190" s="1"/>
       <c r="H190" s="1"/>
@@ -15968,11 +15968,11 @@
         <v>256</v>
       </c>
       <c r="L190" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M190" s="1"/>
       <c r="N190" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O190" s="1" t="s">
         <v>1059</v>
@@ -16326,7 +16326,7 @@
         <v>88</v>
       </c>
       <c r="L197" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M197" s="1" t="s">
         <v>312</v>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="P197" s="1"/>
       <c r="Q197" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R197" s="1" t="s">
         <v>26</v>
@@ -16430,7 +16430,7 @@
         <v>321</v>
       </c>
       <c r="L199" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M199" s="1" t="s">
         <v>1099</v>
@@ -16561,7 +16561,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>26</v>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>29</v>
@@ -16903,7 +16903,7 @@
       </c>
       <c r="P207" s="1"/>
       <c r="Q207" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R207" s="1" t="s">
         <v>26</v>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>26</v>
@@ -17053,13 +17053,13 @@
         <v>33</v>
       </c>
       <c r="G210" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H210" s="1" t="s">
         <v>1175</v>
       </c>
       <c r="I210" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J210" s="1"/>
       <c r="K210" s="1"/>
@@ -17129,7 +17129,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>26</v>
@@ -17176,7 +17176,7 @@
         <v>88</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M212" s="1"/>
       <c r="N212" s="1" t="s">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R212" s="1" t="s">
         <v>26</v>
@@ -17243,7 +17243,7 @@
       </c>
       <c r="P213" s="1"/>
       <c r="Q213" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R213" s="1" t="s">
         <v>26</v>
@@ -17307,7 +17307,7 @@
       </c>
       <c r="P214" s="1"/>
       <c r="Q214" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R214" s="1" t="s">
         <v>26</v>
@@ -17338,7 +17338,7 @@
         <v>26</v>
       </c>
       <c r="F215" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="G215" s="1" t="s">
         <v>43</v>
@@ -17362,14 +17362,14 @@
         <v>1208</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="O215" s="1" t="s">
         <v>1211</v>
       </c>
       <c r="P215" s="1"/>
       <c r="Q215" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R215" s="1" t="s">
         <v>26</v>
@@ -17433,7 +17433,7 @@
         <v>1220</v>
       </c>
       <c r="Q216" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R216" s="1" t="s">
         <v>26</v>
@@ -17581,7 +17581,7 @@
         <v>1238</v>
       </c>
       <c r="K219" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="L219" s="1" t="s">
         <v>216</v>
@@ -17709,7 +17709,7 @@
         <v>1251</v>
       </c>
       <c r="Q221" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R221" s="1" t="s">
         <v>26</v>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R222" s="1" t="s">
         <v>26</v>
@@ -17829,7 +17829,7 @@
         <v>1266</v>
       </c>
       <c r="Q223" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>26</v>
@@ -17891,7 +17891,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -17938,7 +17938,7 @@
         <v>321</v>
       </c>
       <c r="L225" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M225" s="1" t="s">
         <v>1276</v>
@@ -17951,7 +17951,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>26</v>
@@ -17998,7 +17998,7 @@
         <v>88</v>
       </c>
       <c r="L226" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M226" s="1" t="s">
         <v>1284</v>
@@ -18073,7 +18073,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>26</v>
@@ -18131,7 +18131,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>26</v>
@@ -18191,7 +18191,7 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R229" s="1" t="s">
         <v>26</v>
@@ -18229,13 +18229,13 @@
         <v>255</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H230" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J230" s="1" t="s">
         <v>1305</v>
@@ -18257,7 +18257,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>26</v>
@@ -18295,7 +18295,7 @@
         <v>1200</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H231" s="1"/>
       <c r="I231" s="1"/>
@@ -18410,7 +18410,7 @@
         <v>1011</v>
       </c>
       <c r="L233" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M233" s="1" t="s">
         <v>1322</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>26</v>
@@ -18470,7 +18470,7 @@
         <v>1011</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1328</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>26</v>
@@ -18683,7 +18683,7 @@
         <v>29</v>
       </c>
       <c r="U237" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V237" s="1" t="s">
         <v>1349</v>
@@ -18789,7 +18789,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>26</v>
@@ -18827,13 +18827,13 @@
         <v>33</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H240" s="1" t="s">
         <v>1366</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J240" s="1" t="s">
         <v>1367</v>
@@ -18903,7 +18903,7 @@
         <v>1376</v>
       </c>
       <c r="K241" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="L241" s="1" t="s">
         <v>216</v>
@@ -18991,7 +18991,7 @@
         <v>29</v>
       </c>
       <c r="U242" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V242" s="1" t="s">
         <v>1387</v>
@@ -19032,7 +19032,7 @@
         <v>1392</v>
       </c>
       <c r="L243" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M243" s="1" t="s">
         <v>1393</v>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>26</v>
@@ -19417,7 +19417,7 @@
       </c>
       <c r="P249" s="1"/>
       <c r="Q249" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R249" s="1" t="s">
         <v>26</v>
@@ -19481,7 +19481,7 @@
       </c>
       <c r="P250" s="1"/>
       <c r="Q250" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>26</v>
@@ -19585,7 +19585,7 @@
         <v>1453</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L252" s="1" t="s">
         <v>570</v>
@@ -19639,13 +19639,13 @@
         <v>33</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H253" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J253" s="1" t="s">
         <v>1459</v>
@@ -19667,7 +19667,7 @@
       </c>
       <c r="P253" s="1"/>
       <c r="Q253" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R253" s="1" t="s">
         <v>26</v>
@@ -19725,7 +19725,7 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R254" s="1" t="s">
         <v>26</v>
@@ -19774,7 +19774,7 @@
         <v>1471</v>
       </c>
       <c r="L255" s="1" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M255" s="1" t="s">
         <v>1467</v>
@@ -19787,7 +19787,7 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R255" s="1" t="s">
         <v>26</v>
@@ -19911,7 +19911,7 @@
       </c>
       <c r="P257" s="1"/>
       <c r="Q257" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R257" s="1" t="s">
         <v>29</v>
@@ -19985,7 +19985,7 @@
         <v>29</v>
       </c>
       <c r="U258" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V258" s="1" t="s">
         <v>1500</v>
@@ -20033,7 +20033,7 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R259" s="1" t="s">
         <v>26</v>
@@ -20091,7 +20091,7 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R260" s="1" t="s">
         <v>26</v>
@@ -20149,7 +20149,7 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R261" s="1" t="s">
         <v>26</v>
@@ -20209,7 +20209,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>26</v>
@@ -20401,7 +20401,7 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R265" s="1" t="s">
         <v>26</v>
@@ -20555,13 +20555,13 @@
         <v>33</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H268" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J268" s="1" t="s">
         <v>1565</v>
@@ -20634,7 +20634,7 @@
         <v>1576</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1577</v>
@@ -20659,7 +20659,7 @@
         <v>29</v>
       </c>
       <c r="U269" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V269" s="1" t="s">
         <v>1579</v>
@@ -20769,7 +20769,7 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R271" s="1" t="s">
         <v>26</v>
@@ -20813,10 +20813,10 @@
         <v>1591</v>
       </c>
       <c r="K272" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1589</v>
@@ -20865,19 +20865,19 @@
         <v>270</v>
       </c>
       <c r="G273" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H273" s="1" t="s">
         <v>1600</v>
       </c>
       <c r="I273" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J273" s="1" t="s">
         <v>1601</v>
       </c>
       <c r="K273" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L273" s="1" t="s">
         <v>1602</v>
@@ -20931,19 +20931,19 @@
         <v>270</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1600</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>1601</v>
       </c>
       <c r="K274" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="L274" s="1" t="s">
         <v>1602</v>
@@ -21035,7 +21035,7 @@
         <v>29</v>
       </c>
       <c r="U275" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V275" s="1" t="s">
         <v>1617</v>
@@ -21074,7 +21074,7 @@
         <v>1384</v>
       </c>
       <c r="L276" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="M276" s="1" t="s">
         <v>1622</v>
@@ -21099,7 +21099,7 @@
         <v>29</v>
       </c>
       <c r="U276" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V276" s="1" t="s">
         <v>1624</v>
@@ -21133,10 +21133,10 @@
         <v>1629</v>
       </c>
       <c r="K277" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L277" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M277" s="1" t="s">
         <v>1627</v>
@@ -21193,10 +21193,10 @@
         <v>1629</v>
       </c>
       <c r="K278" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L278" s="1" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="M278" s="1" t="s">
         <v>1634</v>
@@ -21283,7 +21283,7 @@
         <v>29</v>
       </c>
       <c r="U279" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V279" s="1" t="s">
         <v>1645</v>
@@ -21335,7 +21335,7 @@
       </c>
       <c r="P280" s="1"/>
       <c r="Q280" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R280" s="1" t="s">
         <v>26</v>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="P281" s="1"/>
       <c r="Q281" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R281" s="1" t="s">
         <v>26</v>
@@ -21409,7 +21409,7 @@
         <v>29</v>
       </c>
       <c r="U281" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="V281" s="1" t="s">
         <v>1664</v>
@@ -21521,7 +21521,7 @@
         <v>29</v>
       </c>
       <c r="U283" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="V283" s="1" t="s">
         <v>1677</v>
@@ -21620,7 +21620,7 @@
         <v>1693</v>
       </c>
       <c r="L285" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M285" s="1" t="s">
         <v>1690</v>
@@ -21693,7 +21693,7 @@
       </c>
       <c r="P286" s="1"/>
       <c r="Q286" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>26</v>
